--- a/table_buildup.xlsx
+++ b/table_buildup.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dscshap3808\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dscshap3808\Documents\my_scripts_new\play1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1509E196-BEDB-43AC-A0D9-D59FE96E6239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAB54F34-A07D-4760-A259-4E3F65BFB348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="820" yWindow="-110" windowWidth="18490" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
   <si>
     <t>字段中文名</t>
   </si>
@@ -256,6 +256,14 @@
   </si>
   <si>
     <t>1/4quantile的误差比例</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚类中心1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>聚类1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -275,23 +283,27 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -695,7 +707,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>46</v>
@@ -709,7 +721,7 @@
         <v>22</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>47</v>
@@ -726,7 +738,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -737,10 +749,10 @@
         <v>24</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -751,7 +763,7 @@
         <v>25</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>50</v>
@@ -779,7 +791,7 @@
         <v>27</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>52</v>
@@ -793,7 +805,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>53</v>
@@ -821,7 +833,7 @@
         <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>55</v>
@@ -835,7 +847,7 @@
         <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>67</v>
@@ -849,7 +861,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>56</v>
@@ -863,7 +875,7 @@
         <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>57</v>
@@ -877,7 +889,7 @@
         <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>58</v>
@@ -905,7 +917,7 @@
         <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>60</v>
@@ -919,7 +931,7 @@
         <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>61</v>
@@ -933,7 +945,7 @@
         <v>38</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>62</v>
@@ -947,7 +959,7 @@
         <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>63</v>
@@ -961,7 +973,7 @@
         <v>40</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>64</v>
@@ -975,7 +987,7 @@
         <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>65</v>
@@ -989,7 +1001,7 @@
         <v>42</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>66</v>
@@ -1003,7 +1015,7 @@
         <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>68</v>
@@ -1017,7 +1029,7 @@
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>69</v>
